--- a/notebooks/Ale/rf_feature_importance_filtered.xlsx
+++ b/notebooks/Ale/rf_feature_importance_filtered.xlsx
@@ -86,7 +86,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,7 +96,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -198,9 +198,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -209,6 +206,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,1024 +574,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sector: Advanced Manufacturing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>🟢 Good (R²≥0.30 / F1≥0.65)   🟡 Marginal (R²0.10–0.29 / F1 0.50–0.64)   🔴 Not recommended  |  Features: top 80% cumulative importance (min 2, max 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>REGRESSION — Location Quotient (LQ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>⚠️  CAGR (continuous growth) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Dependent Variable</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>R² (best)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Importance</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Cumul.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>lq_emp</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>0.2354</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0.2668</v>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Place Conditions</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="n"/>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>45.4%</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.1397</v>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>59.3%</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.0815</v>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>67.5%</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>0.06759999999999999</v>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>74.3%</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>lq_bus</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>0.4266</v>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0.2995</v>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.2273</v>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>52.7%</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0.1805</v>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>70.7%</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.1213</v>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>82.9%</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>BINARY CLASSIFICATION — LQ and CAGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Dependent Variable</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>F1 (best)</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Importance</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Cumul.</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>0.6549</v>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.2668</v>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Place Conditions</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>45.4%</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.1397</v>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>59.3%</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.0815</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>67.5%</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.06759999999999999</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>74.3%</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n">
-        <v>0.7536</v>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.2995</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.2273</v>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>52.7%</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0.1805</v>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>70.7%</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0.1213</v>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>82.9%</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>0.5316</v>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.2854</v>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>28.5%</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0.1174</v>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>40.3%</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>Place Conditions</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.1148</v>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>51.8%</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>fe_and_skills_participation</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0.0902</v>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>60.8%</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0.06859999999999999</v>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>67.6%</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>0.6999</v>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0.4042</v>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>40.4%</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>48.8%</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>active_enterprises</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0.0634</v>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>55.2%</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Total stock of active businesses in the LAD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>new_enterprises</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0.0603</v>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>61.2%</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Number of new businesses registered in the LAD in a given year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>67.0%</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C20:C24"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="C31:C35"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1608,7 +590,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sector: Creative Industries</t>
+          <t>Sector: Advanced Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1629,7 +611,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>⚠️  CAGR (continuous growth) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
+          <t>⚠️  Growth (gd) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
         </is>
       </c>
     </row>
@@ -1681,10 +663,10 @@
           <t>lq_emp</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>0.6433</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
@@ -1695,11 +677,845 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.3591</v>
+        <v>0.2553</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>25.5%</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.2009</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>45.6%</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Place Conditions</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>60.3%</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>69.8%</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>lq_bus</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>61.2%</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>82.1%</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Dependent Variable</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>F1 (best)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Cumul.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>0.7157</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>25.5%</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.2009</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>45.6%</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Place Conditions</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>60.3%</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>69.8%</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>61.2%</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>82.1%</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>0.4878</v>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>❌ Not recommended</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>❌ Insufficient F1 — features not shown</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="15" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>44.2%</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>65.3%</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>72.6%</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="C31:C35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sector: Creative Industries</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>🟢 Good (R²≥0.30 / F1≥0.65)   🟡 Marginal (R²0.10–0.29 / F1 0.50–0.64)   🔴 Not recommended  |  Features: top 80% cumulative importance (min 2, max 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>REGRESSION — Location Quotient (LQ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>⚠️  Growth (gd) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Dependent Variable</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>R² (best)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Cumul.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>lq_emp</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.6341</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1723,11 +1539,11 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.344</v>
+        <v>0.2578</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1742,460 +1558,460 @@
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1031</v>
+        <v>0.1953</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>89.2%</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
           <t>Entrepreneurial Discovery</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_starts</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>0.4563</v>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>45.6%</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="E11" s="9" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Number of apprenticeship starts in the area per period.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_achievements</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>0.2683</v>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>72.5%</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="E12" s="9" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>74.7%</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0.0848</v>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>80.9%</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>86.6%</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14"/>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>BINARY CLASSIFICATION — LQ and CAGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Dependent Variable</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>F1 (best)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Importance</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Cumul.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>0.5909</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="B18" s="16" t="n">
+        <v>0.5911</v>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_achievements</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0.3591</v>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>35.9%</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="E18" s="9" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>32.2%</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_starts</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>70.3%</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="E19" s="9" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>58.0%</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Number of apprenticeship starts in the area per period.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.1031</v>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>80.6%</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>77.5%</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>89.2%</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Entrepreneurial Discovery</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>0.7997</v>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="B23" s="7" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_starts</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>0.4563</v>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>45.6%</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="E23" s="9" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Number of apprenticeship starts in the area per period.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_achievements</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>0.2683</v>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>72.5%</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="E24" s="9" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>74.7%</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.0848</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>80.9%</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>86.6%</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>0.5703</v>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
+    <row r="26"/>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.1254</v>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Place Conditions</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.1212</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>24.7%</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>28.8%</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Entrepreneurial Discovery</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>36.0%</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -2205,43 +2021,43 @@
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1021</v>
+        <v>0.1422</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Place Conditions</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.0854</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -2255,182 +2071,238 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>59.8%</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>0.6276</v>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>65.7%</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.4741</v>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>47.4%</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>fe_and_skills_participation</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0.1189</v>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>59.3%</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>22.6%</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>high_growth_enterprises</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.0585</v>
+        <v>0.2191</v>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>4g_area_coverage</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.0463</v>
+        <v>0.1004</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>62.7%</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>70.1%</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
           <t>Connectivity &amp; Accessibility</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>Share of geographic area with outdoor 4G mobile coverage from at least one operator.</t>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Share of premises with access to gigabit-capable broadband.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A33:A37"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B25:B29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B27:B31"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="C25:C29"/>
-    <mergeCell ref="C31:C35"/>
-    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C18:C21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2479,7 +2351,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>⚠️  CAGR (continuous growth) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
+          <t>⚠️  Growth (gd) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
         </is>
       </c>
     </row>
@@ -2531,23 +2403,23 @@
           <t>lq_emp</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>-10.1142</v>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="n">
+        <v>-3.0207</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient R² — features not shown</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="16" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7"/>
     <row r="8">
@@ -2556,30 +2428,30 @@
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>-0.0019</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="n">
+        <v>-0.2215</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient R² — features not shown</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="16" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>BINARY CLASSIFICATION — LQ and CAGR</t>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
         </is>
       </c>
     </row>
@@ -2631,23 +2503,23 @@
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="16" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="15" t="n"/>
     </row>
     <row r="14"/>
     <row r="15">
@@ -2656,50 +2528,50 @@
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="16" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="15" t="n"/>
     </row>
     <row r="16"/>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>0.7562</v>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>0.7477</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.138</v>
+        <v>0.2626</v>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2709,7 +2581,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
@@ -2719,43 +2591,43 @@
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1305</v>
+        <v>0.1827</v>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1295</v>
+        <v>0.1246</v>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -2765,35 +2637,35 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1211</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Accessibility</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -2803,15 +2675,15 @@
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.0997</v>
+        <v>0.0741</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -2821,7 +2693,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
@@ -2829,28 +2701,28 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="16" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2915,7 +2787,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>⚠️  CAGR (continuous growth) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
+          <t>⚠️  Growth (gd) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
         </is>
       </c>
     </row>
@@ -2967,25 +2839,25 @@
           <t>lq_emp</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>0.5264</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.2649</v>
+        <v>0.3423</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -3005,25 +2877,25 @@
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.1571</v>
+        <v>0.2461</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -3033,43 +2905,43 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1333</v>
+        <v>0.1082</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1156</v>
+        <v>0.0975</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -3079,25 +2951,25 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="11" t="n"/>
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0843</v>
+        <v>0.062</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -3107,7 +2979,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
@@ -3118,10 +2990,10 @@
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>0.5769</v>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="B12" s="7" t="n">
+        <v>0.6281</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
@@ -3132,11 +3004,11 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.2538</v>
+        <v>0.2724</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -3156,15 +3028,15 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.209</v>
+        <v>0.2596</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -3188,11 +3060,11 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1953</v>
+        <v>0.1918</v>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -3212,15 +3084,15 @@
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.0735</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -3240,25 +3112,25 @@
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.0726</v>
+        <v>0.0536</v>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3139,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BINARY CLASSIFICATION — LQ and CAGR</t>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
         </is>
       </c>
     </row>
@@ -3319,25 +3191,25 @@
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>0.6395</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="B21" s="16" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.2649</v>
+        <v>0.3423</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -3357,25 +3229,25 @@
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1571</v>
+        <v>0.2461</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -3385,43 +3257,43 @@
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.1333</v>
+        <v>0.1082</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1156</v>
+        <v>0.0975</v>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -3431,25 +3303,25 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="11" t="n"/>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.0843</v>
+        <v>0.062</v>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -3459,7 +3331,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
@@ -3470,10 +3342,10 @@
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
-        <v>0.7824</v>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>0.7271</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
@@ -3484,11 +3356,11 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.2538</v>
+        <v>0.2724</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -3508,15 +3380,15 @@
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.209</v>
+        <v>0.2596</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -3540,11 +3412,11 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.1953</v>
+        <v>0.1918</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -3564,15 +3436,15 @@
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.0735</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -3592,25 +3464,25 @@
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.0726</v>
+        <v>0.0536</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -3618,38 +3490,38 @@
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>0.5278</v>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.3378</v>
+        <v>0.3322</v>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -3659,25 +3531,25 @@
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.1838</v>
+        <v>0.1537</v>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Place Conditions</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
         </is>
       </c>
     </row>
@@ -3687,81 +3559,81 @@
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>net_additions</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1156</v>
+        <v>0.0881</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Place Conditions</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>active_enterprises</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0822</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Total stock of active businesses in the LAD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="11" t="n"/>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.0517</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses ceasing to trade in the LAD in a given year.</t>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
         </is>
       </c>
     </row>
@@ -3769,38 +3641,38 @@
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>0.6052999999999999</v>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.2774</v>
+        <v>0.2325</v>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
@@ -3810,25 +3682,25 @@
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.2042</v>
+        <v>0.2321</v>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -3838,53 +3710,53 @@
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>active_enterprises</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.0912</v>
+        <v>0.1249</v>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Total stock of active businesses in the LAD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="10" t="n"/>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>net_additions</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.0864</v>
+        <v>0.0843</v>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Place Conditions</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
@@ -3894,25 +3766,25 @@
       <c r="C43" s="11" t="n"/>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3989,7 +3861,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>⚠️  CAGR (continuous growth) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
+          <t>⚠️  Growth (gd) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
         </is>
       </c>
     </row>
@@ -4041,468 +3913,568 @@
           <t>lq_emp</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>0.06320000000000001</v>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient R² — features not shown</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="16" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7"/>
-    <row r="8">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>0.07870000000000001</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="16" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>71.8%</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>79.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>84.1%</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Dependent Variable</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>F1 (best)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Cumul.</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>❌ Insufficient R² — features not shown</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="16" t="n"/>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>BINARY CLASSIFICATION — LQ and CAGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Dependent Variable</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>F1 (best)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Importance</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Cumul.</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>❌ Insufficient F1 — features not shown</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="16" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>❌ Not recommended</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>❌ Insufficient F1 — features not shown</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="16" t="n"/>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>0.5538</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="15" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>31.1%</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Share of premises with access to gigabit-capable broadband.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_starts</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.0949</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>49.6%</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.08110000000000001</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>New firm formation as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>related_variety</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>New firm formation as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>coverage_4g</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>68.7%</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Share of geographic area with outdoor 4G mobile coverage from at least one operator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>75.3%</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Place Conditions</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>24.8%</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>4g_area_coverage</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.1044</v>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>35.2%</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Share of geographic area with outdoor 4G mobile coverage from at least one operator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.09379999999999999</v>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>44.6%</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.0926</v>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>53.9%</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>0.7032</v>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>26.6%</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>net_additions</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.1554</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>42.1%</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Place Conditions</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>4g_area_coverage</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.1348</v>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Share of geographic area with outdoor 4G mobile coverage from at least one operator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.07969999999999999</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>70.7%</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B26:B30"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="C26:C30"/>
     <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C20:C24"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A20:A24"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="A26:A30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4551,7 +4523,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>⚠️  CAGR (continuous growth) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
+          <t>⚠️  Growth (gd) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
         </is>
       </c>
     </row>
@@ -4603,23 +4575,23 @@
           <t>lq_emp</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient R² — features not shown</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="16" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7"/>
     <row r="8" ht="45" customHeight="1">
@@ -4628,35 +4600,35 @@
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>0.2576</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="16" t="n">
+        <v>0.2203</v>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.3967</v>
+        <v>0.3355</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
@@ -4666,43 +4638,43 @@
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.2789</v>
+        <v>0.2067</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0975</v>
+        <v>0.174</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -4712,35 +4684,35 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses ceasing to trade in the LAD in a given year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="11" t="n"/>
       <c r="B11" s="11" t="n"/>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1697</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Number of new businesses registered in the LAD in a given year.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4721,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BINARY CLASSIFICATION — LQ and CAGR</t>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
         </is>
       </c>
     </row>
@@ -4801,23 +4773,23 @@
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>0.06610000000000001</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B16" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="16" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="n"/>
     </row>
     <row r="17"/>
     <row r="18">
@@ -4826,116 +4798,116 @@
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
-        <v>0.4848</v>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="16" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19"/>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>0.5379</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>0.5324</v>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.2679</v>
+        <v>0.1458</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Place Conditions</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1744</v>
+        <v>0.1328</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Number of new businesses registered in the LAD in a given year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1116</v>
+        <v>0.1184</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Accessibility</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -4945,15 +4917,15 @@
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.1175</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -4963,25 +4935,25 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="11" t="n"/>
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.1086</v>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -4991,7 +4963,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses ceasing to trade in the LAD in a given year.</t>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
         </is>
       </c>
     </row>
@@ -4999,66 +4971,66 @@
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n">
-        <v>0.8435</v>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>0.8405</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.3217</v>
+        <v>0.384</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>active_enterprises</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1125</v>
+        <v>0.1055</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Total stock of active businesses in the LAD.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -5068,15 +5040,15 @@
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>new_enterprises</t>
+          <t>enterprise_birth_rate</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1095</v>
+        <v>0.0934</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -5086,7 +5058,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Number of new businesses registered in the LAD in a given year.</t>
+          <t>New firm formation as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
@@ -5096,25 +5068,25 @@
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Connectivity &amp; Accessibility</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses ceasing to trade in the LAD in a given year.</t>
+          <t>Share of premises with access to gigabit-capable broadband.</t>
         </is>
       </c>
     </row>
@@ -5124,25 +5096,25 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>related_variety</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.0732</v>
+        <v>0.075</v>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5213,7 +5185,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>⚠️  CAGR (continuous growth) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
+          <t>⚠️  Growth (gd) not shown in regression — R² ≈ 0 across all sectors. Use binary classification instead.</t>
         </is>
       </c>
     </row>
@@ -5259,69 +5231,69 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>lq_emp</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>0.4524</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>enterprise_high_growth_rate</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.3188</v>
+        <v>0.2639</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.2857</v>
+        <v>0.2286</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Number of apprenticeship starts in the area per period.</t>
         </is>
       </c>
     </row>
@@ -5331,15 +5303,15 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.0912</v>
+        <v>0.1434</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -5353,88 +5325,88 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.0586</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="11" t="n"/>
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>broadband_availability</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0437</v>
+        <v>0.0727</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Accessibility</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>0.6956</v>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="B12" s="7" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.3298</v>
+        <v>0.4169</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -5444,25 +5416,25 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.2067</v>
+        <v>0.2665</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -5472,7 +5444,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Number of apprenticeship starts in the area per period.</t>
         </is>
       </c>
     </row>
@@ -5482,43 +5454,43 @@
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1596</v>
+        <v>0.1027</v>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.0885</v>
+        <v>0.0513</v>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -5528,114 +5500,114 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.0383</v>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>82.3%</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
-        </is>
-      </c>
-    </row>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17"/>
-    <row r="18"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>BINARY CLASSIFICATION — LQ and CAGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Dependent Variable</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>F1 (best)</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Importance</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Cumul.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>26.4%</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>0.6143999999999999</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.3188</v>
+        <v>0.2286</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -5655,71 +5627,71 @@
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>high_growth_enterprises</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.2857</v>
+        <v>0.1434</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Human Capital</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Number of businesses classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>gcse_by_age_19</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.0912</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.0586</v>
+        <v>0.0727</v>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -5729,64 +5701,64 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.0437</v>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>79.8%</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>0.8056</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.3298</v>
+        <v>0.2665</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -5806,15 +5778,15 @@
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>level_3+_qualifications</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.2067</v>
+        <v>0.1027</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -5824,148 +5796,148 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>83.7%</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_high_growth_rate</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
           <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0.1596</v>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>69.6%</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0.0885</v>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>78.5%</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.0383</v>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>82.3%</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>cagr_emp_binary</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>0.5805</v>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.1007</v>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>10.1%</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.095</v>
+        <v>0.0949</v>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -5975,25 +5947,25 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>fe_and_skills_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.095</v>
+        <v>0.0827</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -6003,242 +5975,186 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0.09370000000000001</v>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>38.4%</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>0.6373</v>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>deaths_of_enterprises</t>
+          <t>apprenticeship_starts</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.0907</v>
+        <v>0.1537</v>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeship starts in the area per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>43.9%</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
           <t>Entrepreneurial Discovery</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Number of businesses ceasing to trade in the LAD in a given year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>cagr_bus_binary</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>0.5972</v>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0.2363</v>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>23.6%</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="10" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>active_enterprises</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.181</v>
+        <v>0.1074</v>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
+          <t>Human Capital</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>65.0%</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
           <t>Entrepreneurial Discovery</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Total stock of active businesses in the LAD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="10" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>gcse_by_age_19</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.1103</v>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>52.8%</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>level_3+_qualifications</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.1056</v>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>63.3%</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>broadband_availability</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0.08459999999999999</v>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>71.8%</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>Connectivity &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>Share of premises with access to gigabit-capable broadband.</t>
+          <t>New firm formation as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="C21:C25"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C26:C29"/>
     <mergeCell ref="B6:B10"/>
-    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B37:B41"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="C12:C15"/>
     <mergeCell ref="C6:C10"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="B31:B35"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B21:B25"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="C31:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Ale/rf_feature_importance_filtered.xlsx
+++ b/notebooks/Ale/rf_feature_importance_filtered.xlsx
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,109 +673,109 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.2553</v>
+        <v>0.2632</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.2009</v>
+        <v>0.2418</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Place Conditions</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1464</v>
+        <v>0.1552</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Place Attractiveness</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.0953</v>
+        <v>0.0931</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Labour Market Conditions</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+          <t>Share of economically active residents who are unemployed and seeking work.</t>
         </is>
       </c>
     </row>
@@ -785,25 +785,25 @@
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0428</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -824,198 +824,198 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.3331</v>
+        <v>0.3895</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.2785</v>
+        <v>0.3559</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>79.6%</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity &amp; Agglomeration</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents able to cycle to employment within a defined time/distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>83.0%</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Dependent Variable</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>F1 (best)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Cumul.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>0.7363</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
           <t>Derived Variables</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>82.1%</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Dependent Variable</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>F1 (best)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Importance</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Cumul.</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>0.7157</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.2553</v>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>25.5%</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.2009</v>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>45.6%</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Place Conditions</t>
-        </is>
-      </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1025,25 @@
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1464</v>
+        <v>0.2418</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
@@ -1053,110 +1053,110 @@
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>housing_net_additions</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.0953</v>
+        <v>0.1552</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Place Attractiveness</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0931</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Labour Market Conditions</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+          <t>Share of economically active residents who are unemployed and seeking work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>79.6%</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B26" s="7" t="n">
         <v>0.7923</v>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.3331</v>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.2785</v>
+        <v>0.3895</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -1166,30 +1166,30 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.209</v>
+        <v>0.3559</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -1198,205 +1198,261 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>79.6%</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity &amp; Agglomeration</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents able to cycle to employment within a defined time/distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>83.0%</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>gd_emp_binary</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B31" s="12" t="n">
         <v>0.4878</v>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="15" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="15" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>gd_bus_binary</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B33" s="16" t="n">
         <v>0.572</v>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.2928</v>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>29.3%</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>44.2%</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1198</v>
+        <v>0.2299</v>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+          <t>Share of working-age residents able to cycle to employment within a defined time/distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.091</v>
+        <v>0.1373</v>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Share of working-age residents who can access a defined number of employment sites within a set travel time by public transport.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.0736</v>
+        <v>0.1117</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>fe_participation</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>56.7%</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>broadband</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>65.5%</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity &amp; Agglomeration</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Share of premises with access to gigabit-capable broadband.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C26:C29"/>
     <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="C12:C15"/>
     <mergeCell ref="C6:C10"/>
-    <mergeCell ref="C19:C23"/>
-    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C33:C37"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="B26:B29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1491,7 +1547,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>lq_emp</t>
@@ -1507,53 +1563,53 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.322</v>
+        <v>0.4218</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>Share of working-age residents who can access a defined number of employment sites within a set travel time by public transport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.2578</v>
+        <v>0.1575</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Share of working-age residents able to cycle to employment within a defined time/distance.</t>
         </is>
       </c>
     </row>
@@ -1567,16 +1623,16 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1953</v>
+        <v>0.1419</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -1585,31 +1641,31 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9">
       <c r="A9" s="11" t="n"/>
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.1173</v>
+        <v>0.1175</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1677,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.757</v>
+        <v>0.7662</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -1630,53 +1686,53 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.4402</v>
+        <v>0.6246</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.3065</v>
+        <v>0.115</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -1686,25 +1742,25 @@
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.1193</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Share of working-age residents who can access a defined number of employment sites within a set travel time by public transport.</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1815,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>lq_emp_binary</t>
@@ -1775,53 +1831,53 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.322</v>
+        <v>0.4218</v>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>Share of working-age residents who can access a defined number of employment sites within a set travel time by public transport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.2578</v>
+        <v>0.1575</v>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Share of working-age residents able to cycle to employment within a defined time/distance.</t>
         </is>
       </c>
     </row>
@@ -1835,16 +1891,16 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1953</v>
+        <v>0.1419</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1853,31 +1909,31 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21">
       <c r="A21" s="11" t="n"/>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1173</v>
+        <v>0.1175</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
@@ -1898,53 +1954,53 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.4402</v>
+        <v>0.6246</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.3065</v>
+        <v>0.115</v>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -1954,30 +2010,30 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>transport_to_employer</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.1193</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Share of working-age residents who can access a defined number of employment sites within a set travel time by public transport.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>gd_emp_binary</t>
@@ -1993,25 +2049,25 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.2879</v>
+        <v>0.1748</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
@@ -2025,16 +2081,16 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1422</v>
+        <v>0.1526</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Place Conditions</t>
+          <t>Place Attractiveness</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -2053,16 +2109,16 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1161</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -2071,64 +2127,64 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="45" customHeight="1">
+    <row r="30">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="11" t="n"/>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>enterprise_birth_rate</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+          <t>New firm formation as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
     <row r="32"/>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>gd_bus_binary</t>
@@ -2144,53 +2200,53 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.226</v>
+        <v>0.1717</v>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.2191</v>
+        <v>0.1583</v>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
@@ -2204,16 +2260,16 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.1004</v>
+        <v>0.1031</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2222,31 +2278,31 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0818</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>TBD — count of fee-capped higher education institutions located in the LAD.</t>
         </is>
       </c>
     </row>
@@ -2260,16 +2316,16 @@
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.074</v>
+        <v>0.0757</v>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Accessibility</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2429,7 +2485,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>-0.2215</v>
+        <v>-0.2177</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -2554,7 +2610,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.7477</v>
+        <v>0.7534</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -2567,16 +2623,16 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.2626</v>
+        <v>0.3504</v>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -2585,31 +2641,31 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1827</v>
+        <v>0.1318</v>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Labour Market Conditions</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of economically active residents who are unemployed and seeking work.</t>
         </is>
       </c>
     </row>
@@ -2619,81 +2675,81 @@
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.1246</v>
+        <v>0.1069</v>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.1042</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>Share of premises with access to gigabit-capable broadband.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="11" t="n"/>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.0741</v>
+        <v>0.0897</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2833,7 +2889,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>lq_emp</t>
@@ -2849,25 +2905,25 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.3423</v>
+        <v>0.4584</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
@@ -2877,25 +2933,25 @@
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.2461</v>
+        <v>0.1767</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -2905,120 +2961,120 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1082</v>
+        <v>0.1433</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.0975</v>
+        <v>0.0515</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>85.6%</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>lq_bus</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B11" s="7" t="n">
         <v>0.6281</v>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>✅ Recommended</t>
         </is>
       </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>37.1%</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.2724</v>
+        <v>0.29</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -3028,556 +3084,539 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>75.9%</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>83.5%</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Dependent Variable</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>F1 (best)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Cumul.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>lq_emp_binary</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
           <t>nvq_level3</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>53.2%</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="E20" s="9" t="n">
+        <v>0.1767</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>63.5%</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>gcse_age19</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>apprenticeship_achievements</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>0.1918</v>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>72.4%</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="E22" s="9" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>83.0%</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0.7315</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>37.1%</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>66.1%</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>gcse_age19</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>0.06759999999999999</v>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>79.1%</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="E26" s="9" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>75.9%</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.0536</v>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>84.5%</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Dependent Variable</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>F1 (best)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Importance</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Cumul.</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>lq_emp_binary</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>0.5423</v>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>83.5%</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>0.5278</v>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.3423</v>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>34.2%</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.2461</v>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.1082</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>69.7%</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Derived Variables</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>79.4%</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>fe_participation</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>85.6%</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>0.7271</v>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.2724</v>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>27.2%</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>53.2%</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0.1918</v>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>72.4%</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
+          <t>n_universities_feecap_lad</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>TBD — count of fee-capped higher education institutions located in the LAD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Place Attractiveness</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
           <t>gcse_age19</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>0.06759999999999999</v>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>79.1%</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="E32" s="9" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>68.4%</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.0536</v>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>84.5%</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
     <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>gd_emp_binary</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n">
-        <v>0.5278</v>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>73.9%</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.3322</v>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>33.2%</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>housing_net_additions</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0.1537</v>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>48.6%</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>Place Conditions</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.0881</v>
+        <v>0.3534</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+          <t>TBD — count of fee-capped higher education institutions located in the LAD.</t>
         </is>
       </c>
     </row>
@@ -3587,232 +3626,137 @@
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.0822</v>
+        <v>0.1891</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0629</v>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
           <t>Derived Variables</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
     <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>gd_bus_binary</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>0.6452</v>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.2325</v>
+        <v>0.0521</v>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0.2321</v>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>46.5%</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.1249</v>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>59.0%</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_death_rate</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.0843</v>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>67.4%</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>74.6%</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="C21:C25"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B11:B14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="B33:B37"/>
-    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B35:B39"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A39:A43"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B21:B25"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C24:C27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3824,7 +3768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3932,7 +3876,7 @@
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7"/>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>lq_bus</t>
@@ -3948,25 +3892,25 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.3752</v>
+        <v>0.504</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>TBD — count of fee-capped higher education institutions located in the LAD.</t>
         </is>
       </c>
     </row>
@@ -3976,25 +3920,25 @@
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.343</v>
+        <v>0.0649</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Derived Variables</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
@@ -4004,215 +3948,215 @@
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0767</v>
+        <v>0.0603</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>drive_to_employer</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.0463</v>
+        <v>0.0564</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Share of working-age residents who can access employment sites within a set drive time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>size_micro_share</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>73.9%</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Derived Variables</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
     <row r="13"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Dependent Variable</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>F1 (best)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Importance</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Cumul.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B17" s="12" t="n">
         <v>0.16</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B19" s="12" t="n">
         <v>0.2105</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="15" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="15" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>gd_emp_binary</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B21" s="16" t="n">
         <v>0.5462</v>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>⚠️ Marginal</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.1892</v>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
           <t>broadband</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1216</v>
+        <v>0.1358</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Accessibility</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -4221,31 +4165,31 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.0949</v>
+        <v>0.1096</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
@@ -4255,110 +4199,110 @@
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.0905</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>42.6%</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Place Attractiveness</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>drive_to_employer</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity &amp; Agglomeration</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents who can access employment sites within a set drive time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
           <t>enterprise_birth_rate</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>0.08110000000000001</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>57.7%</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>New firm formation as a share of the active enterprise stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>gd_bus_binary</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.3526</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>35.3%</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_birth_rate</t>
-        </is>
-      </c>
       <c r="E27" s="9" t="n">
-        <v>0.1832</v>
+        <v>0.1705</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -4382,16 +4326,16 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.0755</v>
+        <v>0.1287</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -4400,81 +4344,109 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
+    <row r="29">
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>coverage_4g</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1268</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Accessibility</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Share of geographic area with outdoor 4G mobile coverage from at least one operator.</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>housing_net_additions</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Place Conditions</t>
+          <t>Place Attractiveness</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_death_rate</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>61.0%</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Discovery</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B26:B30"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="C26:C30"/>
     <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="B21:B25"/>
+    <mergeCell ref="C21:C25"/>
+    <mergeCell ref="A27:A31"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="D17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4486,7 +4458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4614,16 +4586,16 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.3355</v>
+        <v>0.4286</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -4632,21 +4604,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>related_variety</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.2067</v>
+        <v>0.2777</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -4656,202 +4628,202 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.174</v>
+        <v>0.1255</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0.1697</v>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>88.6%</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
           <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12"/>
-    <row r="13"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Dependent Variable</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>F1 (best)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Importance</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Cumul.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="B15" s="12" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="15" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>lq_bus_binary</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B17" s="12" t="n">
         <v>0.4941</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>❌ Not recommended</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>❌ Insufficient F1 — features not shown</t>
         </is>
       </c>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="15" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>0.5324</v>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>cycle_to_employer</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Connectivity &amp; Agglomeration</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents able to cycle to employment within a defined time/distance.</t>
+        </is>
+      </c>
+    </row>
     <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>gd_emp_binary</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>0.5324</v>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>housing_net_additions</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1458</v>
+        <v>0.1255</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Place Conditions</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
@@ -4865,16 +4837,16 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.1328</v>
+        <v>0.1237</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -4889,120 +4861,120 @@
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
+          <t>housing_net_additions</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Place Attractiveness</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Net annual additions to the local housing stock (new builds minus demolitions/conversions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
           <t>nvq_level3</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>0.1184</v>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>39.7%</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="E23" s="9" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.1175</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>51.4%</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>62.3%</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+    <row r="24"/>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0.8405</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>nvq_level3</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>25.4%</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>enterprise_birth_rate</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>36.5%</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Entrepreneurial Discovery</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>gd_bus_binary</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>0.8405</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>38.4%</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
+          <t>New firm formation as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
@@ -5012,25 +4984,25 @@
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.1055</v>
+        <v>0.0968</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
         </is>
       </c>
     </row>
@@ -5040,103 +5012,75 @@
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>enterprise_birth_rate</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.0934</v>
+        <v>0.0832</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>New firm formation as a share of the active enterprise stock.</t>
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>broadband</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.077</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Connectivity &amp; Accessibility</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Share of premises with access to gigabit-capable broadband.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>related_variety</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>73.5%</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>Derived Variables</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Degree to which a LAD's industrial mix contains sectors that are technologically or capability-adjacent to IS8 sectors.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B26:B30"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="C26:C30"/>
     <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="C25:C29"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="A19:A23"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="D17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5148,7 +5092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5231,7 +5175,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>lq_emp</t>
@@ -5247,137 +5191,137 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>n_universities_feecap_lad</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.2639</v>
+        <v>0.249</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>TBD — count of fee-capped higher education institutions located in the LAD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.2286</v>
+        <v>0.2477</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>size_micro_share</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1434</v>
+        <v>0.1315</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Derived Variables</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>Share of local IS8 businesses with 0–9 employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="11" t="n"/>
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0727</v>
+        <v>0.0667</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
@@ -5402,16 +5346,16 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.4169</v>
+        <v>0.5142</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -5426,48 +5370,48 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>apprenticeship_achievements</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.2665</v>
+        <v>0.1467</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Number of apprenticeships successfully completed in the area.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>gcse_age19</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1027</v>
+        <v>0.1426</v>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -5476,299 +5420,268 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_achievements</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>83.7%</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16"/>
-    <row r="17"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>BINARY CLASSIFICATION — LQ and Growth (gd)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Dependent Variable</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>F1 (best)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Importance</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Cumul.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>lq_emp_binary</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>0.5046</v>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_high_growth_rate</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.2639</v>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>26.4%</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
+      <c r="B19" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>❌ Not recommended</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>❌ Insufficient F1 — features not shown</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="15" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>lq_bus_binary</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>0.8056</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
+        </is>
+      </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.2286</v>
+        <v>0.5142</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
+          <t>apprenticeship_achievements</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>66.1%</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Number of apprenticeships successfully completed in the area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
           <t>gcse_age19</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>0.1434</v>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="E23" s="9" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>80.4%</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>gd_emp_binary</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>enterprise_death_rate</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>0.07969999999999999</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>71.6%</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="E25" s="9" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>14.1%</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Entrepreneurial Discovery</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.0727</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>78.8%</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
     <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>lq_bus_binary</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>0.8056</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>✅ Recommended</t>
-        </is>
-      </c>
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>fe_participation</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.4169</v>
+        <v>0.119</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_starts</t>
+          <t>nvq_level3</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.2665</v>
+        <v>0.1136</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
+          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
         </is>
       </c>
     </row>
@@ -5782,16 +5695,16 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1027</v>
+        <v>0.1032</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -5806,54 +5719,54 @@
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>apprenticeship_achievements</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.0513</v>
+        <v>0.074</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Number of apprenticeships successfully completed in the area.</t>
+          <t>Share of premises with access to gigabit-capable broadband.</t>
         </is>
       </c>
     </row>
     <row r="30"/>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>gd_emp_binary</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>0.5854</v>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
+          <t>gd_bus_binary</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>0.6677</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>✅ Recommended</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>enterprise_high_growth_rate</t>
+          <t>enterprise_death_rate</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>0.1612</v>
+        <v>0.1637</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -5863,35 +5776,35 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Share of active firms classified as high-growth (20%+ employment/turnover growth p.a. over 3 years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>enterprise_death_rate</t>
+          <t>gcse_age19</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.1447</v>
+        <v>0.1324</v>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Entrepreneurial Discovery</t>
+          <t>Knowledge Base</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
+          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
         </is>
       </c>
     </row>
@@ -5901,25 +5814,25 @@
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>nvq_level3</t>
+          <t>drive_to_employer</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.1344</v>
+        <v>0.1028</v>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
+          <t>Share of working-age residents who can access employment sites within a set drive time.</t>
         </is>
       </c>
     </row>
@@ -5929,231 +5842,78 @@
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>fe_participation</t>
+          <t>cycle_to_employer</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.0949</v>
+        <v>0.101</v>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Connectivity &amp; Agglomeration</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Rate of participation in Further Education and skills programmes among working-age adults.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t>Share of working-age residents able to cycle to employment within a defined time/distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="11" t="n"/>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>gcse_age19</t>
+          <t>enterprise_birth_rate</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.0827</v>
+        <v>0.0924</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Human Capital</t>
+          <t>Entrepreneurial Discovery</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>gd_bus_binary</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>0.6373</v>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ Marginal</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>apprenticeship_starts</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0.1537</v>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Number of apprenticeship starts in the area per period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>gcse_age19</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0.1507</v>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>30.4%</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Share of young people achieving a standard pass (grade 4+) in English and Maths GCSEs by age 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_death_rate</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>43.9%</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Businesses ceasing to trade as a share of the active enterprise stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>nvq_level3</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0.1074</v>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>54.7%</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>Human Capital</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Share of working-age residents holding qualifications at NVQ Level 3 or above (A-level equivalent or higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>enterprise_birth_rate</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.1034</v>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>65.0%</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Discovery</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
           <t>New firm formation as a share of the active enterprise stock.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C26:C29"/>
+  <mergeCells count="21">
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="B6:B10"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B37:B41"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="C12:C15"/>
     <mergeCell ref="C6:C10"/>
-    <mergeCell ref="C37:C41"/>
     <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B12:B14"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="B21:B23"/>
     <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C20:C24"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="C25:C29"/>
     <mergeCell ref="C31:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
